--- a/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_15_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem5_SineHighFreq/Res/Comparativa_15_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.249996</v>
+        <v>0.249999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         <v>0.667222</v>
       </c>
       <c r="J2" t="n">
-        <v>0.249928</v>
+        <v>0.249925</v>
       </c>
       <c r="K2" t="n">
         <v>0.5600000000000001</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_9.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,42 +682,42 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.245348</v>
+        <v>0.249995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.555041</v>
+        <v>0.500625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.598002</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.575721</v>
+        <v>0.667222</v>
       </c>
       <c r="J3" t="n">
-        <v>0.251751</v>
+        <v>0.249926</v>
       </c>
       <c r="K3" t="n">
-        <v>0.594595</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.589286</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.591928</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,23 +753,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_19.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_5.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
       </c>
       <c r="AA3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249999</v>
+        <v>0.245749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E4" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.500625</v>
+        <v>0.551887</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.58427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.667222</v>
+        <v>0.567617</v>
       </c>
       <c r="J4" t="n">
-        <v>0.249925</v>
+        <v>0.251685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59633</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.580357</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.588235</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_9.txt</t>
+          <t>_2_15_1_1790733069_16.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.243798</v>
+        <v>0.249996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.558891</v>
+        <v>0.500625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.604245</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.580684</v>
+        <v>0.667222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.252015</v>
+        <v>0.249931</v>
       </c>
       <c r="K5" t="n">
-        <v>0.582569</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.566964</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.574661</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_9.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_14.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2442</v>
+        <v>0.249997</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.560606</v>
+        <v>0.500625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.600499</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.579867</v>
+        <v>0.667222</v>
       </c>
       <c r="J6" t="n">
-        <v>0.252402</v>
+        <v>0.249941</v>
       </c>
       <c r="K6" t="n">
-        <v>0.587963</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.566964</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.577273</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_18.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_17.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>15</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.245882</v>
+        <v>0.249978</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5282559999999999</v>
+        <v>0.502259</v>
       </c>
       <c r="H7" t="n">
-        <v>0.536829</v>
+        <v>0.832709</v>
       </c>
       <c r="I7" t="n">
-        <v>0.532508</v>
+        <v>0.6265849999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.252702</v>
+        <v>0.250002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.566502</v>
+        <v>0.544073</v>
       </c>
       <c r="L7" t="n">
-        <v>0.513393</v>
+        <v>0.799107</v>
       </c>
       <c r="M7" t="n">
-        <v>0.538642</v>
+        <v>0.647378</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_13.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_12.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.249994</v>
+        <v>0.246063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E8" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.500625</v>
+        <v>0.54717</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.579276</v>
       </c>
       <c r="I8" t="n">
-        <v>0.667222</v>
+        <v>0.562765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.249927</v>
+        <v>0.252059</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.593607</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.580357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.586907</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_6.txt</t>
+          <t>_2_15_1_1790733069_12.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>15</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1288,42 +1288,42 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249999</v>
+        <v>0.245348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.500625</v>
+        <v>0.555041</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.598002</v>
       </c>
       <c r="I9" t="n">
-        <v>0.667222</v>
+        <v>0.575721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.249934</v>
+        <v>0.251751</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.594595</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.589286</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.591928</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_0.txt</t>
+          <t>_2_15_1_1790733069_19.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>15</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1389,42 +1389,42 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.24578</v>
+        <v>0.249988</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.529132</v>
+        <v>0.500625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.555556</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.542022</v>
+        <v>0.667222</v>
       </c>
       <c r="J10" t="n">
-        <v>0.252147</v>
+        <v>0.249935</v>
       </c>
       <c r="K10" t="n">
-        <v>0.564815</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.544643</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.554545</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,23 +1460,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_14.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_11.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.249997</v>
+        <v>0.245919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E11" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.500625</v>
+        <v>0.554642</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.589263</v>
       </c>
       <c r="I11" t="n">
-        <v>0.667222</v>
+        <v>0.571429</v>
       </c>
       <c r="J11" t="n">
-        <v>0.249919</v>
+        <v>0.251565</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5944700000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.575893</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.5850340000000001</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,23 +1561,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_18.txt</t>
+          <t>_2_15_1_1790733069_7.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>15</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.249978</v>
+        <v>0.246149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E12" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.502259</v>
+        <v>0.53076</v>
       </c>
       <c r="H12" t="n">
-        <v>0.832709</v>
+        <v>0.5493130000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6265849999999999</v>
+        <v>0.5398770000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.250002</v>
+        <v>0.251871</v>
       </c>
       <c r="K12" t="n">
-        <v>0.544073</v>
+        <v>0.580189</v>
       </c>
       <c r="L12" t="n">
-        <v>0.799107</v>
+        <v>0.549107</v>
       </c>
       <c r="M12" t="n">
-        <v>0.647378</v>
+        <v>0.5642200000000001</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_12.txt</t>
+          <t>_2_15_1_1790733069_17.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>15</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.246001</v>
+        <v>0.245491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.534118</v>
+        <v>0.5538459999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.566792</v>
+        <v>0.58427</v>
       </c>
       <c r="I13" t="n">
-        <v>0.54997</v>
+        <v>0.568651</v>
       </c>
       <c r="J13" t="n">
-        <v>0.251453</v>
+        <v>0.252357</v>
       </c>
       <c r="K13" t="n">
-        <v>0.571429</v>
+        <v>0.587678</v>
       </c>
       <c r="L13" t="n">
         <v>0.553571</v>
       </c>
       <c r="M13" t="n">
-        <v>0.562358</v>
+        <v>0.570115</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_0.txt</t>
+          <t>_2_15_1_1790733069_6.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1894,42 +1894,42 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.245749</v>
+        <v>0.250002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.551887</v>
+        <v>0.500625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.58427</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.567617</v>
+        <v>0.667222</v>
       </c>
       <c r="J15" t="n">
-        <v>0.251685</v>
+        <v>0.249917</v>
       </c>
       <c r="K15" t="n">
-        <v>0.59633</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.580357</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0.588235</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_16.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_8.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
       </c>
       <c r="AA15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.244637</v>
+        <v>0.245882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.557716</v>
+        <v>0.5282559999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.573034</v>
+        <v>0.536829</v>
       </c>
       <c r="I16" t="n">
-        <v>0.565271</v>
+        <v>0.532508</v>
       </c>
       <c r="J16" t="n">
-        <v>0.252208</v>
+        <v>0.252702</v>
       </c>
       <c r="K16" t="n">
-        <v>0.588517</v>
+        <v>0.566502</v>
       </c>
       <c r="L16" t="n">
-        <v>0.549107</v>
+        <v>0.513393</v>
       </c>
       <c r="M16" t="n">
-        <v>0.568129</v>
+        <v>0.538642</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_11.txt</t>
+          <t>_2_15_1_1790733069_13.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,42 +2096,42 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.249961</v>
+        <v>0.245926</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E17" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.515702</v>
+        <v>0.55814</v>
       </c>
       <c r="H17" t="n">
-        <v>0.779026</v>
+        <v>0.599251</v>
       </c>
       <c r="I17" t="n">
-        <v>0.620587</v>
+        <v>0.577965</v>
       </c>
       <c r="J17" t="n">
-        <v>0.249882</v>
+        <v>0.251618</v>
       </c>
       <c r="K17" t="n">
-        <v>0.577419</v>
+        <v>0.597285</v>
       </c>
       <c r="L17" t="n">
-        <v>0.799107</v>
+        <v>0.589286</v>
       </c>
       <c r="M17" t="n">
-        <v>0.670412</v>
+        <v>0.593258</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,23 +2167,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_19.txt</t>
+          <t>_2_15_1_1790733069_4.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>15</v>
       </c>
       <c r="AA17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2197,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.245919</v>
+        <v>0.250003</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.554642</v>
+        <v>0.500625</v>
       </c>
       <c r="H18" t="n">
-        <v>0.589263</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.571429</v>
+        <v>0.667222</v>
       </c>
       <c r="J18" t="n">
-        <v>0.251565</v>
+        <v>0.249926</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5944700000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.575893</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5850340000000001</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_7.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_2.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>15</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.24564</v>
+        <v>0.246001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.551804</v>
+        <v>0.534118</v>
       </c>
       <c r="H19" t="n">
-        <v>0.59176</v>
+        <v>0.566792</v>
       </c>
       <c r="I19" t="n">
-        <v>0.571084</v>
+        <v>0.54997</v>
       </c>
       <c r="J19" t="n">
-        <v>0.251746</v>
+        <v>0.251453</v>
       </c>
       <c r="K19" t="n">
-        <v>0.600917</v>
+        <v>0.571429</v>
       </c>
       <c r="L19" t="n">
-        <v>0.584821</v>
+        <v>0.553571</v>
       </c>
       <c r="M19" t="n">
-        <v>0.59276</v>
+        <v>0.562358</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_8.txt</t>
+          <t>_2_15_1_1790733069_0.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.245491</v>
+        <v>0.2442</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5538459999999999</v>
+        <v>0.560606</v>
       </c>
       <c r="H20" t="n">
-        <v>0.58427</v>
+        <v>0.600499</v>
       </c>
       <c r="I20" t="n">
-        <v>0.568651</v>
+        <v>0.579867</v>
       </c>
       <c r="J20" t="n">
-        <v>0.252357</v>
+        <v>0.252402</v>
       </c>
       <c r="K20" t="n">
-        <v>0.587678</v>
+        <v>0.587963</v>
       </c>
       <c r="L20" t="n">
-        <v>0.553571</v>
+        <v>0.566964</v>
       </c>
       <c r="M20" t="n">
-        <v>0.570115</v>
+        <v>0.577273</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_6.txt</t>
+          <t>_2_15_1_1790733069_18.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.249996</v>
+        <v>0.246217</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E21" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.500625</v>
+        <v>0.5161289999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.519351</v>
       </c>
       <c r="I21" t="n">
-        <v>0.667222</v>
+        <v>0.5177349999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.249972</v>
+        <v>0.252697</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5603860000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.517857</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.538283</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_15.txt</t>
+          <t>_2_15_1_1790733069_3.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>15</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.24514</v>
+        <v>0.244637</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2618,25 +2618,25 @@
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.555687</v>
+        <v>0.557716</v>
       </c>
       <c r="H22" t="n">
-        <v>0.585518</v>
+        <v>0.573034</v>
       </c>
       <c r="I22" t="n">
-        <v>0.570213</v>
+        <v>0.565271</v>
       </c>
       <c r="J22" t="n">
-        <v>0.252291</v>
+        <v>0.252208</v>
       </c>
       <c r="K22" t="n">
-        <v>0.580189</v>
+        <v>0.588517</v>
       </c>
       <c r="L22" t="n">
         <v>0.549107</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5642200000000001</v>
+        <v>0.568129</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_2.txt</t>
+          <t>_2_15_1_1790733069_11.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.249997</v>
+        <v>0.245674</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E23" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.500625</v>
+        <v>0.527845</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.54432</v>
       </c>
       <c r="I23" t="n">
-        <v>0.667222</v>
+        <v>0.535956</v>
       </c>
       <c r="J23" t="n">
-        <v>0.249941</v>
+        <v>0.25265</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.551724</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.52459</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_17.txt</t>
+          <t>_2_15_1_1790733069_5.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>15</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.249979</v>
+        <v>0.249997</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.498334</v>
+        <v>0.500625</v>
       </c>
       <c r="H24" t="n">
-        <v>0.933833</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6498699999999999</v>
+        <v>0.667222</v>
       </c>
       <c r="J24" t="n">
-        <v>0.249953</v>
+        <v>0.249919</v>
       </c>
       <c r="K24" t="n">
-        <v>0.55643</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.946429</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7008259999999999</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_1.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_18.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.250001</v>
+        <v>0.24514</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E25" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.500625</v>
+        <v>0.555687</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.585518</v>
       </c>
       <c r="I25" t="n">
-        <v>0.667222</v>
+        <v>0.570213</v>
       </c>
       <c r="J25" t="n">
-        <v>0.249924</v>
+        <v>0.252291</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.580189</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.549107</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.5642200000000001</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_10.txt</t>
+          <t>_2_15_1_1790733069_2.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>15</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3005,7 +3005,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.249988</v>
+        <v>0.249991</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>0.667222</v>
       </c>
       <c r="J26" t="n">
-        <v>0.249935</v>
+        <v>0.249921</v>
       </c>
       <c r="K26" t="n">
         <v>0.5600000000000001</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_11.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_16.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3106,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.245398</v>
+        <v>0.249961</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E27" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.550562</v>
+        <v>0.515702</v>
       </c>
       <c r="H27" t="n">
-        <v>0.611735</v>
+        <v>0.779026</v>
       </c>
       <c r="I27" t="n">
-        <v>0.579539</v>
+        <v>0.620587</v>
       </c>
       <c r="J27" t="n">
-        <v>0.252522</v>
+        <v>0.249882</v>
       </c>
       <c r="K27" t="n">
-        <v>0.577586</v>
+        <v>0.577419</v>
       </c>
       <c r="L27" t="n">
-        <v>0.598214</v>
+        <v>0.799107</v>
       </c>
       <c r="M27" t="n">
-        <v>0.587719</v>
+        <v>0.670412</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_10.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_19.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>15</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3207,42 +3207,42 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.246149</v>
+        <v>0.250001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F28" t="n">
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.53076</v>
+        <v>0.500625</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5493130000000001</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5398770000000001</v>
+        <v>0.667222</v>
       </c>
       <c r="J28" t="n">
-        <v>0.251871</v>
+        <v>0.249924</v>
       </c>
       <c r="K28" t="n">
-        <v>0.580189</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>0.549107</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5642200000000001</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,23 +3278,23 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_17.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_10.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>15</v>
       </c>
       <c r="AA28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3308,42 +3308,42 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.249988</v>
+        <v>0.245398</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E29" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.500625</v>
+        <v>0.550562</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.611735</v>
       </c>
       <c r="I29" t="n">
-        <v>0.667222</v>
+        <v>0.579539</v>
       </c>
       <c r="J29" t="n">
-        <v>0.249911</v>
+        <v>0.252522</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.577586</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.598214</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.587719</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,23 +3379,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_7.txt</t>
+          <t>_2_15_1_1790733069_10.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3409,7 +3409,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.249999</v>
+        <v>0.249988</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>0.667222</v>
       </c>
       <c r="J30" t="n">
-        <v>0.249916</v>
+        <v>0.249911</v>
       </c>
       <c r="K30" t="n">
         <v>0.5600000000000001</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_3.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_7.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.245674</v>
+        <v>0.249996</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E31" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.527845</v>
+        <v>0.500625</v>
       </c>
       <c r="H31" t="n">
-        <v>0.54432</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.535956</v>
+        <v>0.667222</v>
       </c>
       <c r="J31" t="n">
-        <v>0.25265</v>
+        <v>0.249972</v>
       </c>
       <c r="K31" t="n">
-        <v>0.551724</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0.52459</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_5.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_15.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>15</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249995</v>
+        <v>0.24578</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.500625</v>
+        <v>0.529132</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.555556</v>
       </c>
       <c r="I32" t="n">
-        <v>0.667222</v>
+        <v>0.542022</v>
       </c>
       <c r="J32" t="n">
-        <v>0.249926</v>
+        <v>0.252147</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.564815</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0.544643</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.554545</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_5.txt</t>
+          <t>_2_15_1_1790733069_14.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>15</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.249991</v>
+        <v>0.249999</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>0.667222</v>
       </c>
       <c r="J33" t="n">
-        <v>0.249921</v>
+        <v>0.249934</v>
       </c>
       <c r="K33" t="n">
         <v>0.5600000000000001</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_16.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_0.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3813,42 +3813,42 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.245926</v>
+        <v>0.249999</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E34" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F34" t="n">
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.55814</v>
+        <v>0.500625</v>
       </c>
       <c r="H34" t="n">
-        <v>0.599251</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.577965</v>
+        <v>0.667222</v>
       </c>
       <c r="J34" t="n">
-        <v>0.251618</v>
+        <v>0.249916</v>
       </c>
       <c r="K34" t="n">
-        <v>0.597285</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>0.589286</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.593258</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,23 +3884,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_3.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z34" t="n">
         <v>15</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -3914,42 +3914,42 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.249996</v>
+        <v>0.243848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E35" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.500625</v>
+        <v>0.54638</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.602996</v>
       </c>
       <c r="I35" t="n">
-        <v>0.667222</v>
+        <v>0.573294</v>
       </c>
       <c r="J35" t="n">
-        <v>0.249931</v>
+        <v>0.251506</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.581081</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.575893</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.578475</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,23 +3985,23 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_14.txt</t>
+          <t>_2_15_1_1790733069_15.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>15</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.250003</v>
+        <v>0.249979</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.500625</v>
+        <v>0.498334</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.933833</v>
       </c>
       <c r="I36" t="n">
-        <v>0.667222</v>
+        <v>0.6498699999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.249926</v>
+        <v>0.249953</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55643</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0.946429</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.7008259999999999</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_2.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_1.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4116,42 +4116,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.246063</v>
+        <v>0.249994</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E37" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.54717</v>
+        <v>0.500625</v>
       </c>
       <c r="H37" t="n">
-        <v>0.579276</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.562765</v>
+        <v>0.667222</v>
       </c>
       <c r="J37" t="n">
-        <v>0.252059</v>
+        <v>0.249927</v>
       </c>
       <c r="K37" t="n">
-        <v>0.593607</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>0.580357</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.586907</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,23 +4187,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_12.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_6.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>15</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4217,42 +4217,42 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.250002</v>
+        <v>0.243798</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F38" t="n">
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.500625</v>
+        <v>0.558891</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0.604245</v>
       </c>
       <c r="I38" t="n">
-        <v>0.667222</v>
+        <v>0.580684</v>
       </c>
       <c r="J38" t="n">
-        <v>0.249934</v>
+        <v>0.252015</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.582569</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0.566964</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.574661</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,23 +4288,23 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_13.txt</t>
+          <t>_2_15_1_1790733069_9.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z38" t="n">
         <v>15</v>
       </c>
       <c r="AA38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.250002</v>
+        <v>0.24564</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790733126</v>
+        <v>1790733069</v>
       </c>
       <c r="E39" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.500625</v>
+        <v>0.551804</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0.59176</v>
       </c>
       <c r="I39" t="n">
-        <v>0.667222</v>
+        <v>0.571084</v>
       </c>
       <c r="J39" t="n">
-        <v>0.249917</v>
+        <v>0.251746</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.600917</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.584821</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7179489999999999</v>
+        <v>0.59276</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790733126_8.txt</t>
+          <t>_2_15_1_1790733069_8.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>15</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,42 +4419,42 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.246217</v>
+        <v>0.250002</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E40" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F40" t="n">
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5161289999999999</v>
+        <v>0.500625</v>
       </c>
       <c r="H40" t="n">
-        <v>0.519351</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5177349999999999</v>
+        <v>0.667222</v>
       </c>
       <c r="J40" t="n">
-        <v>0.252697</v>
+        <v>0.249934</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5603860000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>0.517857</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.538283</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,23 +4490,23 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_3.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_13.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z40" t="n">
         <v>15</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.243848</v>
+        <v>0.249996</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790733069</v>
+        <v>1790733126</v>
       </c>
       <c r="E41" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.54638</v>
+        <v>0.500625</v>
       </c>
       <c r="H41" t="n">
-        <v>0.602996</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.573294</v>
+        <v>0.667222</v>
       </c>
       <c r="J41" t="n">
-        <v>0.251506</v>
+        <v>0.249928</v>
       </c>
       <c r="K41" t="n">
-        <v>0.581081</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>0.575893</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.578475</v>
+        <v>0.7179489999999999</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_15_1_1790733069_15.txt</t>
+          <t>_2_3_3_3_3_3_1_1790733126_4.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>15</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.5699215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01977556368349586</v>
+        <v>0.01977556368349583</v>
       </c>
       <c r="D2" t="n">
         <v>0.593258</v>
@@ -4710,7 +4710,7 @@
         <v>0.7111874499999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01866443052686327</v>
+        <v>0.01866443052686325</v>
       </c>
       <c r="D3" t="n">
         <v>0.7179489999999999</v>
